--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R356-ProfessionRessource.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R356-ProfessionRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="262">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -788,6 +788,18 @@
   </si>
   <si>
     <t>Stomathérapeute</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Infirmier expert en plaies et cicatrisation</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>Sexologue</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2428,30 @@
       </c>
       <c r="D101" s="2"/>
     </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="D102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="D103" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R356-ProfessionRessource.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R356-ProfessionRessource.xlsx
@@ -208,7 +208,7 @@
     <t>08</t>
   </si>
   <si>
-    <t>Médiateur de santé pair</t>
+    <t>Médiateur de santé pair ou de santé communautaire</t>
   </si>
   <si>
     <t>10</t>
